--- a/data/trans_bre/P19C01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 14,58</t>
+          <t>-0,55; 14,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-6,25; 8,39</t>
+          <t>-5,65; 8,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 8,3</t>
+          <t>-6,42; 8,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,56; 16,62</t>
+          <t>-4,86; 16,15</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 40,49</t>
+          <t>-1,28; 38,43</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 20,14</t>
+          <t>-11,75; 20,92</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 16,86</t>
+          <t>-11,36; 17,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-7,77; 27,66</t>
+          <t>-6,54; 26,61</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,54; 10,76</t>
+          <t>0,11; 11,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 12,07</t>
+          <t>0,14; 12,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,73; 11,63</t>
+          <t>-1,56; 10,5</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 18,77</t>
+          <t>-3,38; 18,69</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-2,11; 36,27</t>
+          <t>0,42; 39,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 39,15</t>
+          <t>0,46; 40,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,14; 31,44</t>
+          <t>-3,58; 28,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,17; 32,41</t>
+          <t>-5,18; 29,27</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 7,08</t>
+          <t>-3,92; 6,9</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,21; 13,25</t>
+          <t>1,92; 13,3</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 12,1</t>
+          <t>0,17; 12,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-3,24; 8,18</t>
+          <t>-4,09; 7,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-12,59; 25,37</t>
+          <t>-11,72; 25,46</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,6; 49,87</t>
+          <t>5,91; 48,67</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 32,71</t>
+          <t>0,16; 32,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 14,48</t>
+          <t>-6,3; 13,21</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-3,46; 9,38</t>
+          <t>-2,7; 9,55</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,06; 13,34</t>
+          <t>1,91; 13,85</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 7,48</t>
+          <t>-4,68; 8,69</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 40,53</t>
+          <t>-3,96; 38,83</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 41,91</t>
+          <t>-9,22; 43,36</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,46; 55,03</t>
+          <t>6,4; 60,06</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-9,76; 19,05</t>
+          <t>-10,16; 23,04</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-7,71; 208,48</t>
+          <t>-6,78; 194,83</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,77; 2,34</t>
+          <t>-11,68; 2,3</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 8,79</t>
+          <t>-4,6; 9,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 11,03</t>
+          <t>-4,08; 10,71</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 9,67</t>
+          <t>-0,33; 9,86</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 10,93</t>
+          <t>-39,37; 9,92</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,14; 39,94</t>
+          <t>-16,42; 41,31</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 34,28</t>
+          <t>-10,54; 33,29</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,13; 19,97</t>
+          <t>-0,6; 20,65</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-9,2; 5,55</t>
+          <t>-8,14; 6,29</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-1,35; 12,78</t>
+          <t>-0,9; 12,86</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,91; 7,93</t>
+          <t>-9,74; 7,29</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,73; 4,82</t>
+          <t>-37,75; 4,28</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-35,46; 31,01</t>
+          <t>-30,9; 36,82</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 96,94</t>
+          <t>-6,77; 97,47</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,66; 25,17</t>
+          <t>-24,27; 23,25</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,98; 10,11</t>
+          <t>-72,54; 8,6</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,67; 6,52</t>
+          <t>-10,43; 7,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,62; 12,59</t>
+          <t>-1,97; 12,66</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,44; 12,3</t>
+          <t>-7,3; 12,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 6,15</t>
+          <t>-6,33; 5,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-46,01; 53,04</t>
+          <t>-44,8; 61,65</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 128,41</t>
+          <t>-10,96; 129,29</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-21,06; 49,36</t>
+          <t>-20,75; 48,94</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,07; 16,25</t>
+          <t>-14,13; 14,86</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,38</t>
+          <t>-0,92; 4,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,35</t>
+          <t>2,26; 7,21</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>-0,07; 5,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 13,4</t>
+          <t>-6,45; 12,36</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 15,35</t>
+          <t>-2,99; 14,75</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,15; 25,47</t>
+          <t>7,3; 25,27</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,58</t>
+          <t>-0,16; 13,16</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 29,22</t>
+          <t>-11,11; 26,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C01-Edad-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Edad-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5,49</t>
+          <t>6,63</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>10,03%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 14,11</t>
+          <t>-1,03; 14,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-5,65; 8,61</t>
+          <t>-6,15; 8,46</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,42; 8,35</t>
+          <t>-5,86; 8,84</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 16,15</t>
+          <t>-5,49; 16,9</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,28; 38,43</t>
+          <t>-2,23; 38,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,75; 20,92</t>
+          <t>-12,62; 20,25</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-11,36; 17,22</t>
+          <t>-10,09; 18,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 26,61</t>
+          <t>-7,11; 28,91</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5,01</t>
+          <t>-0,69</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>-1,05%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,11; 11,9</t>
+          <t>0,08; 11,45</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 12,69</t>
+          <t>1,28; 13,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-1,56; 10,5</t>
+          <t>-1,2; 11,17</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-3,38; 18,69</t>
+          <t>-7,75; 6,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,42; 39,51</t>
+          <t>0,18; 38,85</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,46; 40,88</t>
+          <t>3,55; 42,56</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,58; 28,41</t>
+          <t>-2,83; 30,21</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-5,18; 29,27</t>
+          <t>-11,34; 10,52</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,46</t>
+          <t>3,25</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>5,42%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 6,9</t>
+          <t>-4,52; 7,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,92; 13,3</t>
+          <t>3,04; 13,58</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,17; 12,32</t>
+          <t>0,34; 12,49</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 7,46</t>
+          <t>-1,95; 8,86</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-11,72; 25,46</t>
+          <t>-13,49; 26,31</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,91; 48,67</t>
+          <t>9,36; 51,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,16; 32,28</t>
+          <t>0,81; 33,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-6,3; 13,21</t>
+          <t>-3,02; 15,94</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>15,4</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 9,55</t>
+          <t>-2,54; 9,1</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 13,85</t>
+          <t>2,1; 13,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-4,68; 8,69</t>
+          <t>-3,85; 8,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 38,83</t>
+          <t>-2,38; 7,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-9,22; 43,36</t>
+          <t>-8,59; 41,77</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,4; 60,06</t>
+          <t>7,24; 59,21</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 23,04</t>
+          <t>-8,42; 22,73</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-6,78; 194,83</t>
+          <t>-3,81; 13,55</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4,72</t>
+          <t>4,62</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>8,95%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,68; 2,3</t>
+          <t>-11,59; 2,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 9,0</t>
+          <t>-4,04; 9,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-4,08; 10,71</t>
+          <t>-4,08; 10,98</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 9,86</t>
+          <t>-0,27; 9,74</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-39,37; 9,92</t>
+          <t>-39,43; 12,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,42; 41,31</t>
+          <t>-14,38; 40,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 33,29</t>
+          <t>-10,42; 33,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 20,65</t>
+          <t>-0,5; 19,99</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-15,32</t>
+          <t>2,47</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>-30,87%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 6,29</t>
+          <t>-9,12; 5,91</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 12,86</t>
+          <t>-0,97; 12,7</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 7,29</t>
+          <t>-10,32; 7,08</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-37,75; 4,28</t>
+          <t>-2,55; 8,25</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-30,9; 36,82</t>
+          <t>-35,9; 33,22</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-6,77; 97,47</t>
+          <t>-4,94; 93,13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-24,27; 23,25</t>
+          <t>-25,41; 22,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-72,54; 8,6</t>
+          <t>-4,75; 17,65</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-0,32</t>
+          <t>0,14</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-0,78%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 7,85</t>
+          <t>-10,71; 7,03</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,97; 12,66</t>
+          <t>-1,75; 12,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,3; 12,15</t>
+          <t>-8,24; 10,9</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-6,33; 5,62</t>
+          <t>-5,96; 5,44</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-44,8; 61,65</t>
+          <t>-46,25; 56,95</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-10,96; 129,29</t>
+          <t>-10,3; 132,26</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-20,75; 48,94</t>
+          <t>-23,03; 43,59</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-14,13; 14,86</t>
+          <t>-13,1; 14,3</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,24</t>
+          <t>-0,99; 4,32</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,21</t>
+          <t>2,25; 7,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,15</t>
+          <t>-0,41; 5,22</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 12,36</t>
+          <t>-0,4; 4,49</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 14,75</t>
+          <t>-3,12; 15,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>7,3; 25,27</t>
+          <t>7,37; 25,7</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 13,16</t>
+          <t>-0,96; 13,18</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 26,99</t>
+          <t>-0,66; 8,03</t>
         </is>
       </c>
     </row>
